--- a/UnityTableTool/Data/表格规范.xlsx
+++ b/UnityTableTool/Data/表格规范.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="181">
   <si>
     <t>table:types</t>
   </si>
@@ -414,6 +414,9 @@
   </si>
   <si>
     <t>greeting</t>
+  </si>
+  <si>
+    <t>2003#10</t>
   </si>
   <si>
     <t>1|文本#2001#10;2|说明#2002#20</t>
@@ -1878,11 +1881,11 @@
     <col min="13" max="14" width="7.81666666666667" style="12" customWidth="1"/>
     <col min="15" max="15" width="21.725" style="12" customWidth="1"/>
     <col min="16" max="18" width="17.4583333333333" style="12" customWidth="1"/>
-    <col min="19" max="19" width="53.3666666666667" style="12" customWidth="1"/>
+    <col min="19" max="19" width="42.375" style="12" customWidth="1"/>
     <col min="20" max="22" width="12.1833333333333" style="12" customWidth="1"/>
     <col min="23" max="24" width="24.8166666666667" style="12" customWidth="1"/>
     <col min="25" max="26" width="25.0916666666667" style="12" customWidth="1"/>
-    <col min="27" max="27" width="25.725" style="12" customWidth="1"/>
+    <col min="27" max="27" width="29.75" style="12" customWidth="1"/>
     <col min="28" max="28" width="10" style="12" customWidth="1"/>
     <col min="29" max="29" width="9" style="12"/>
     <col min="30" max="30" width="20.6333333333333" style="12" customWidth="1"/>
@@ -2480,12 +2483,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2517,7 +2520,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2526,7 +2529,7 @@
       <c r="F1" s="4"/>
       <c r="G1" s="3"/>
       <c r="H1" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -2536,31 +2539,31 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2577,7 +2580,7 @@
         <v>34</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>22</v>
@@ -2586,7 +2589,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="6"/>
@@ -2599,22 +2602,22 @@
         <v>42</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>62</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="6"/>
@@ -2663,10 +2666,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>94</v>
@@ -2675,25 +2678,25 @@
         <v>80</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>95</v>
@@ -2702,25 +2705,25 @@
         <v>81</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>96</v>
@@ -2729,16 +2732,16 @@
         <v>81</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I9" s="8"/>
     </row>
@@ -2858,10 +2861,10 @@
         <v>110</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2870,13 +2873,13 @@
         <v>10002</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>101</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2898,7 +2901,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2909,13 +2912,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2940,10 +2943,10 @@
         <v>42</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2974,22 +2977,22 @@
         <v>110</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="19"/>
       <c r="B8" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3017,7 +3020,7 @@
   <sheetData>
     <row r="1" ht="30" spans="1:5">
       <c r="A1" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3027,16 +3030,16 @@
     <row r="2" spans="1:5">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3060,10 +3063,10 @@
         <v>42</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>67</v>
@@ -3083,7 +3086,7 @@
     <row r="6" spans="1:5">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>33</v>
@@ -3097,7 +3100,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>37</v>
@@ -3111,7 +3114,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>22</v>
@@ -3125,7 +3128,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>22</v>
@@ -3157,7 +3160,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3168,13 +3171,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3200,10 +3203,10 @@
         <v>42</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3239,7 +3242,7 @@
         <v>1001</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D7" s="7">
         <v>50</v>
@@ -3322,7 +3325,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3333,13 +3336,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3364,10 +3367,10 @@
         <v>42</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3399,25 +3402,25 @@
     <row r="7" spans="1:4">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3438,12 +3441,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3464,12 +3467,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3495,7 +3498,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/UnityTableTool/Data/表格规范.xlsx
+++ b/UnityTableTool/Data/表格规范.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="基础表 所有字段类型" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="180">
   <si>
     <t>table:types</t>
   </si>
@@ -416,9 +416,6 @@
     <t>greeting</t>
   </si>
   <si>
-    <t>2003#10</t>
-  </si>
-  <si>
     <t>1|文本#2001#10;2|说明#2002#20</t>
   </si>
   <si>
@@ -440,10 +437,10 @@
     <t>英文</t>
   </si>
   <si>
-    <t>zh-CN</t>
-  </si>
-  <si>
-    <t>en-US</t>
+    <t>zh_CN</t>
+  </si>
+  <si>
+    <t>en_US</t>
   </si>
   <si>
     <t>你好</t>
@@ -2483,12 +2480,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2517,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2529,7 +2526,7 @@
       <c r="F1" s="4"/>
       <c r="G1" s="3"/>
       <c r="H1" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -2539,31 +2536,31 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2580,7 +2577,7 @@
         <v>34</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>22</v>
@@ -2589,7 +2586,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="6"/>
@@ -2602,22 +2599,22 @@
         <v>42</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>62</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="6"/>
@@ -2666,10 +2663,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>94</v>
@@ -2678,25 +2675,25 @@
         <v>80</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>95</v>
@@ -2705,25 +2702,25 @@
         <v>81</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>177</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>178</v>
       </c>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>96</v>
@@ -2732,16 +2729,16 @@
         <v>81</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>180</v>
-      </c>
       <c r="G9" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I9" s="8"/>
     </row>
@@ -2861,10 +2858,10 @@
         <v>110</v>
       </c>
       <c r="D7" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>111</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2873,13 +2870,13 @@
         <v>10002</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>101</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2901,7 +2898,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2912,13 +2909,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>117</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2943,10 +2940,10 @@
         <v>42</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>119</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2977,22 +2974,22 @@
         <v>110</v>
       </c>
       <c r="C7" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>121</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="19"/>
       <c r="B8" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C8" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>123</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3020,7 +3017,7 @@
   <sheetData>
     <row r="1" ht="30" spans="1:5">
       <c r="A1" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3030,16 +3027,16 @@
     <row r="2" spans="1:5">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3063,10 +3060,10 @@
         <v>42</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>67</v>
@@ -3086,7 +3083,7 @@
     <row r="6" spans="1:5">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>33</v>
@@ -3100,7 +3097,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>37</v>
@@ -3114,7 +3111,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>22</v>
@@ -3128,7 +3125,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>22</v>
@@ -3160,7 +3157,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3171,13 +3168,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>138</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3203,10 +3200,10 @@
         <v>42</v>
       </c>
       <c r="C4" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>140</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3242,7 +3239,7 @@
         <v>1001</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7" s="7">
         <v>50</v>
@@ -3325,7 +3322,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3336,13 +3333,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>138</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3367,10 +3364,10 @@
         <v>42</v>
       </c>
       <c r="C4" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>140</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3402,25 +3399,25 @@
     <row r="7" spans="1:4">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3441,12 +3438,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3467,12 +3464,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3498,7 +3495,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
